--- a/artfynd/A 19369-2026 artfynd.xlsx
+++ b/artfynd/A 19369-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133792573</v>
+        <v>136793529</v>
       </c>
       <c r="B3" t="n">
-        <v>8460</v>
+        <v>58005</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Prästhem, Sm</t>
+          <t>Knutingarp, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500048</v>
+        <v>500121</v>
       </c>
       <c r="R3" t="n">
-        <v>6430314</v>
+        <v>6430189</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +881,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133792573</t>
+          <t>https://artportalen.se/Sighting/136793529</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133792945</v>
+        <v>133792573</v>
       </c>
       <c r="B4" t="n">
-        <v>56904</v>
+        <v>8460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208255</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500050</v>
+        <v>500048</v>
       </c>
       <c r="R4" t="n">
-        <v>6430298</v>
+        <v>6430314</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,62 +994,54 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133792945</t>
+          <t>https://artportalen.se/Sighting/133792573</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119502600</v>
+        <v>133792945</v>
       </c>
       <c r="B5" t="n">
-        <v>99118</v>
+        <v>56904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>208255</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Knutingarp, Sm</t>
+          <t>Prästhem, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500121</v>
+        <v>500050</v>
       </c>
       <c r="R5" t="n">
-        <v>6430189</v>
+        <v>6430298</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1059,12 +1065,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,34 +1079,33 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119502600</t>
+          <t>https://artportalen.se/Sighting/133792945</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133793896</v>
+        <v>119502600</v>
       </c>
       <c r="B6" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,27 +1132,26 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Prästhem, Sm</t>
+          <t>Knutingarp, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500071</v>
+        <v>500121</v>
       </c>
       <c r="R6" t="n">
-        <v>6430213</v>
+        <v>6430189</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1171,12 +1175,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,30 +1189,31 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133793896</t>
+          <t>https://artportalen.se/Sighting/119502600</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133794322</v>
+        <v>133793896</v>
       </c>
       <c r="B7" t="n">
         <v>99195</v>
@@ -1238,7 +1243,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1252,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500054</v>
+        <v>500071</v>
       </c>
       <c r="R7" t="n">
-        <v>6430240</v>
+        <v>6430213</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,13 +1318,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133794322</t>
+          <t>https://artportalen.se/Sighting/133793896</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133796355</v>
+        <v>133794322</v>
       </c>
       <c r="B8" t="n">
         <v>99195</v>
@@ -1347,17 +1352,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Prästhem, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500088</v>
+        <v>500054</v>
       </c>
       <c r="R8" t="n">
-        <v>6430225</v>
+        <v>6430240</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,60 +1429,51 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133796355</t>
+          <t>https://artportalen.se/Sighting/133794322</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133792505</v>
+        <v>133796355</v>
       </c>
       <c r="B9" t="n">
-        <v>106324</v>
+        <v>99195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Prästhem, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500061</v>
+        <v>500088</v>
       </c>
       <c r="R9" t="n">
-        <v>6430311</v>
+        <v>6430225</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,13 +1531,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133792505</t>
+          <t>https://artportalen.se/Sighting/133796355</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133792844</v>
+        <v>133792505</v>
       </c>
       <c r="B10" t="n">
         <v>106324</v>
@@ -1562,7 +1567,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1576,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500050</v>
+        <v>500061</v>
       </c>
       <c r="R10" t="n">
-        <v>6430298</v>
+        <v>6430311</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,16 +1642,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133792844</t>
+          <t>https://artportalen.se/Sighting/133792505</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133793757</v>
+        <v>133792844</v>
       </c>
       <c r="B11" t="n">
-        <v>98060</v>
+        <v>106324</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,34 +1659,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Prästhem, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500102</v>
+        <v>500050</v>
       </c>
       <c r="R11" t="n">
-        <v>6430225</v>
+        <v>6430298</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,6 +1752,108 @@
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133792844</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133793757</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Prästhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>500102</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6430225</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/133793757</t>
         </is>
@@ -1755,6 +1871,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19369-2026 artfynd.xlsx
+++ b/artfynd/A 19369-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136793529</v>
       </c>
       <c r="B3" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19369-2026 artfynd.xlsx
+++ b/artfynd/A 19369-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136793529</v>
       </c>
       <c r="B3" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19369-2026 artfynd.xlsx
+++ b/artfynd/A 19369-2026 artfynd.xlsx
@@ -815,16 +815,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Knutingarp, Sm</t>

--- a/artfynd/A 19369-2026 artfynd.xlsx
+++ b/artfynd/A 19369-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136793529</v>
       </c>
       <c r="B3" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19369-2026 artfynd.xlsx
+++ b/artfynd/A 19369-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136793529</v>
       </c>
       <c r="B3" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19369-2026 artfynd.xlsx
+++ b/artfynd/A 19369-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136793529</v>
       </c>
       <c r="B3" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
